--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -540,6 +540,40 @@
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources[0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v1</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources[1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources[2]</t>
         </is>
       </c>
     </row>
@@ -554,11 +588,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
@@ -594,17 +628,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>name_of_issuer</t>
+          <t>issuer_lei</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1</t>
+          <t>sec.nport.security.v1, sec.nport.security_isin.v1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1</t>
+          <t>sec.nport.security.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -621,25 +655,52 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>name_of_issuer</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v1, sec.nport.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>sec.thirteenf.information_table.security.v1</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>title_of_class</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v1, sec.nport.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>sec.thirteenf.information_table.security.v1</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Kind default</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources</t>
         </is>
@@ -722,11 +783,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -812,6 +873,120 @@
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml rules[0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>nport-security-cusip</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15.1</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>The record's CUSIP is the one a Company holds; and Exactly one Company holds that CUSIP, or none</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml rules[1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>nport-security-isin</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15.1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>The record's ISIN is the one a Company holds; and Exactly one Company holds that ISIN, or none</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml rules[2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>nport-isin-security-isin</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15.1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>The record's ISIN is the one a Company holds; and Exactly one Company holds that ISIN, or none</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml rules[3]</t>
         </is>
       </c>
     </row>
@@ -873,7 +1048,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -891,7 +1066,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -909,7 +1084,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -862,7 +862,7 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>The record's CUSIP is the one a Company holds; and Exactly one Company holds that CUSIP, or none</t>
+          <t>The record's CUSIP is the one a Security holds; and Exactly one Security holds that CUSIP, or none</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>The record's CUSIP is the one a Company holds; and Exactly one Company holds that CUSIP, or none</t>
+          <t>The record's CUSIP is the one a Security holds; and Exactly one Security holds that CUSIP, or none</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>The record's ISIN is the one a Company holds; and Exactly one Company holds that ISIN, or none</t>
+          <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>The record's ISIN is the one a Company holds; and Exactly one Company holds that ISIN, or none</t>
+          <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -574,6 +574,40 @@
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources[2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources[3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources[4]</t>
         </is>
       </c>
     </row>
@@ -783,7 +817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -987,6 +1021,82 @@
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml rules[3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>openfigi-security-cusip</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17.1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>The record's CUSIP is the one a Security holds; and Exactly one Security holds that CUSIP, or none</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml rules[4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>openfigi-security-isin</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17.1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml rules[5]</t>
         </is>
       </c>
     </row>

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>openfigi.security_isin.v1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security_isin.v1</t>
+          <t>sec.nport.security.v1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>sec.nport.security_isin.v1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v1</t>
+          <t>sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -627,7 +627,7 @@
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
@@ -694,12 +694,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v1, sec.nport.security_isin.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -721,12 +721,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v1, sec.nport.security_isin.v1</t>
+          <t>sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1</t>
+          <t>sec.nport.security.v1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -622,10 +622,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -689,12 +689,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>name_of_issuer</t>
+          <t>market_sector</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -716,25 +716,133 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>name_of_issuer</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>security_type</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>security_type2</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>share_class_figi</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>title_of_class</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>sec.nport.security.v1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Kind default</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources</t>
         </is>

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -568,7 +568,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -585,29 +585,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security_isin.v1</t>
+          <t>sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources[3]</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>sec.thirteenf.information_table.security.v1</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml defaults.sources[4]</t>
         </is>
       </c>
     </row>
@@ -667,12 +650,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1, sec.nport.security_isin.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -721,7 +704,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -829,12 +812,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
+          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -925,11 +908,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -1031,12 +1014,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-20.1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -1069,12 +1052,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-20.1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -1102,28 +1085,28 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>nport-isin-security-isin</t>
+          <t>openfigi-security-cusip</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-17.1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security_isin.v1</t>
+          <t>openfigi.security.v1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
+          <t>The record's CUSIP is the one a Security holds; and Exactly one Security holds that CUSIP, or none</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>mint</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1140,7 +1123,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>openfigi-security-cusip</t>
+          <t>openfigi-security-isin</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1150,13 +1133,13 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security_isin.v1</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>The record's CUSIP is the one a Security holds; and Exactly one Security holds that CUSIP, or none</t>
+          <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1167,44 +1150,6 @@
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml rules[4]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>openfigi-security-isin</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17.1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security_isin.v1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>wait</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml rules[5]</t>
         </is>
       </c>
     </row>

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -568,7 +568,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -585,29 +585,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security_isin.v1</t>
+          <t>sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources[3]</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>sec.thirteenf.information_table.security.v1</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml defaults.sources[4]</t>
         </is>
       </c>
     </row>
@@ -622,10 +605,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -667,12 +650,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1, sec.nport.security_isin.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -689,12 +672,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>name_of_issuer</t>
+          <t>market_sector</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -716,25 +699,133 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>name_of_issuer</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>security_type</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>security_type2</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>share_class_figi</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>title_of_class</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security.v1, sec.nport.security_isin.v1, sec.thirteenf.information_table.security.v1</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security.v1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Kind default</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources</t>
         </is>
@@ -817,11 +908,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -923,12 +1014,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-20.1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -961,12 +1052,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-20.1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -994,28 +1085,28 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>nport-isin-security-isin</t>
+          <t>openfigi-security-cusip</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-17.1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security_isin.v1</t>
+          <t>openfigi.security.v1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
+          <t>The record's CUSIP is the one a Security holds; and Exactly one Security holds that CUSIP, or none</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>mint</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1032,7 +1123,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>openfigi-security-cusip</t>
+          <t>openfigi-security-isin</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1042,13 +1133,13 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security_isin.v1</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>The record's CUSIP is the one a Security holds; and Exactly one Security holds that CUSIP, or none</t>
+          <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1059,44 +1150,6 @@
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml rules[4]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>openfigi-security-isin</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17.1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security_isin.v1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>wait</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml rules[5]</t>
         </is>
       </c>
     </row>

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -645,17 +645,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>issuer_lei</t>
+          <t>market_sector</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2</t>
+          <t>openfigi.security.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -672,12 +672,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>market_sector</t>
+          <t>name_of_issuer</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -699,12 +699,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>name_of_issuer</t>
+          <t>security_type</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>security_type</t>
+          <t>security_type2</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>security_type2</t>
+          <t>share_class_figi</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -780,17 +780,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>share_class_figi</t>
+          <t>title_of_class</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -799,33 +799,6 @@
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>title_of_class</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security.v2</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources</t>
         </is>

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -605,10 +605,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -753,17 +753,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>share_class_figi</t>
+          <t>title_of_class</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -772,33 +772,6 @@
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>title_of_class</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security.v2</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources</t>
         </is>

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -605,10 +605,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -645,17 +645,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>issuer_lei</t>
+          <t>market_sector</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2</t>
+          <t>openfigi.security.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -672,12 +672,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>market_sector</t>
+          <t>name_of_issuer</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -699,12 +699,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>name_of_issuer</t>
+          <t>security_type</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>security_type</t>
+          <t>security_type2</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -753,17 +753,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>security_type2</t>
+          <t>title_of_class</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -772,60 +772,6 @@
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>share_class_figi</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>openfigi.security.v1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>title_of_class</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>sec.nport.security.v2</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources</t>
         </is>

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -753,25 +753,52 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>share_class</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>title_of_class</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>sec.nport.security.v2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Kind default</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources</t>
         </is>

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>security-2026-10-14.1</t>
+          <t>security-2026-10-23.openfigi-first</t>
         </is>
       </c>
     </row>
@@ -881,11 +881,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17.1</t>
+          <t>2026-10-23.1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>mint</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>openfigi-security-isin</t>
+          <t>openfigi-isin-security-cusip</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17.1</t>
+          <t>2026-10-23.1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1112,17 +1112,55 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>The record's CUSIP is the one a Security holds; and Exactly one Security holds that CUSIP, or none</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml rules[4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>openfigi-security-isin</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23.1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security_isin.v1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>wait</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml rules[4]</t>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml rules[5]</t>
         </is>
       </c>
     </row>

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>security-2026-10-23.openfigi-first</t>
+          <t>security-2026-10-24.isin-source-code</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v1</t>
+          <t>openfigi.security_isin.v2</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v2</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v2, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v2</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v1</t>
+          <t>openfigi.security.v1, openfigi.security_isin.v2</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v1</t>
+          <t>openfigi.security_isin.v2</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v1</t>
+          <t>openfigi.security_isin.v2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>security-2026-10-24.isin-source-code</t>
+          <t>security-2026-10-25.one-openfigi-load</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v2</t>
+          <t>sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -574,23 +574,6 @@
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources[2]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>sec.thirteenf.information_table.security.v1</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml defaults.sources[3]</t>
         </is>
       </c>
     </row>
@@ -610,7 +593,7 @@
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
@@ -650,12 +633,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v2</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -677,12 +660,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v2, sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+          <t>openfigi.security.v3, sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -704,12 +687,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v2</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -731,12 +714,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1, openfigi.security_isin.v2</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -758,12 +741,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2</t>
+          <t>sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -785,12 +768,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2, sec.thirteenf.information_table.security.v1</t>
+          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2</t>
+          <t>sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -885,7 +868,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -1063,12 +1046,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23.1</t>
+          <t>2026-10-25.1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v1</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -1096,28 +1079,28 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>openfigi-isin-security-cusip</t>
+          <t>openfigi-security-isin</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24.1</t>
+          <t>2026-10-25.1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v2</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>The record's CUSIP is the one a Security holds; and Exactly one Security holds that CUSIP, or none</t>
+          <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>mint</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1134,23 +1117,23 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>openfigi-security-isin</t>
+          <t>openfigi-security-figi</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24.1</t>
+          <t>2026-10-25.1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security_isin.v2</t>
+          <t>openfigi.security.v3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
+          <t>The record's FIGI is the one a Security holds; and Exactly one Security holds that FIGI, or none</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20.1</t>
+          <t>2026-10-26.1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -970,7 +970,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20.1</t>
+          <t>2026-10-26.1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -970,7 +970,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20.1</t>
+          <t>2026-10-26.1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20.1</t>
+          <t>2026-10-26.1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>security-2026-10-25.one-openfigi-load</t>
+          <t>security-2026-10-26.figi-merges-securities</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25.1</t>
+          <t>2026-10-26.1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>security-2026-10-26.figi-merges-securities</t>
+          <t>security-2026-10-26.filed-cusip-binds-first</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26.1</t>
+          <t>2026-10-26.2</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>security-2026-10-26.filed-cusip-binds-first</t>
+          <t>security-2026-10-26.filed-figi-finds</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -932,7 +932,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14.1</t>
+          <t>2026-10-26.1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -965,28 +965,28 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>nport-security-cusip</t>
+          <t>thirteenf-security-figi</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26.2</t>
+          <t>2026-10-26.1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2</t>
+          <t>sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>The record's CUSIP is the one a Security holds; and Exactly one Security holds that CUSIP, or none</t>
+          <t>The record's FIGI is the one a Security holds; and Exactly one Security holds that FIGI, or none</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>mint</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>nport-security-isin</t>
+          <t>nport-security-cusip</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26.1</t>
+          <t>2026-10-26.2</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
+          <t>The record's CUSIP is the one a Security holds; and Exactly one Security holds that CUSIP, or none</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1041,23 +1041,23 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>openfigi-security-cusip</t>
+          <t>nport-security-isin</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25.1</t>
+          <t>2026-10-26.1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v3</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>The record's CUSIP is the one a Security holds; and Exactly one Security holds that CUSIP, or none</t>
+          <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>openfigi-security-isin</t>
+          <t>openfigi-security-cusip</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
+          <t>The record's CUSIP is the one a Security holds; and Exactly one Security holds that CUSIP, or none</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>openfigi-security-figi</t>
+          <t>openfigi-security-isin</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26.1</t>
+          <t>2026-10-25.1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1133,17 +1133,55 @@
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml rules[5]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>openfigi-security-figi</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26.1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v3</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>The record's FIGI is the one a Security holds; and Exactly one Security holds that FIGI, or none</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>mint</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml rules[5]</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml rules[6]</t>
         </is>
       </c>
     </row>

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -932,7 +932,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26.1</t>
+          <t>2026-10-14.1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>security-2026-10-26.filed-cusip-binds-first</t>
+          <t>security-2026-10-26.filed-figi-finds</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -965,28 +965,28 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>nport-security-cusip</t>
+          <t>thirteenf-security-figi</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26.2</t>
+          <t>2026-10-26.1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>sec.nport.security.v2</t>
+          <t>sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>The record's CUSIP is the one a Security holds; and Exactly one Security holds that CUSIP, or none</t>
+          <t>The record's FIGI is the one a Security holds; and Exactly one Security holds that FIGI, or none</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>mint</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>nport-security-isin</t>
+          <t>nport-security-cusip</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26.1</t>
+          <t>2026-10-26.2</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
+          <t>The record's CUSIP is the one a Security holds; and Exactly one Security holds that CUSIP, or none</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1041,23 +1041,23 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>openfigi-security-cusip</t>
+          <t>nport-security-isin</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25.1</t>
+          <t>2026-10-26.1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v3</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>The record's CUSIP is the one a Security holds; and Exactly one Security holds that CUSIP, or none</t>
+          <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>openfigi-security-isin</t>
+          <t>openfigi-security-cusip</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
+          <t>The record's CUSIP is the one a Security holds; and Exactly one Security holds that CUSIP, or none</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>openfigi-security-figi</t>
+          <t>openfigi-security-isin</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26.1</t>
+          <t>2026-10-25.1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1133,17 +1133,55 @@
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>The record's ISIN is the one a Security holds; and Exactly one Security holds that ISIN, or none</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml rules[5]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>openfigi-security-figi</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26.1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v3</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>The record's FIGI is the one a Security holds; and Exactly one Security holds that FIGI, or none</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>mint</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/security.yaml rules[5]</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml rules[6]</t>
         </is>
       </c>
     </row>

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>security-2026-10-26.filed-figi-finds</t>
+          <t>security-2026-10-27.filed-figi-on</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14.1</t>
+          <t>2026-10-27.1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/rules/merge/kinds/security.xlsx
+++ b/rules/merge/kinds/security.xlsx
@@ -588,10 +588,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -628,17 +628,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>market_sector</t>
+          <t>asset_category</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v3</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v3</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -655,17 +655,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>name_of_issuer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v3, sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v3</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -682,17 +682,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>security_type</t>
+          <t>derivative_category</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v3</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v3</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>security_type2</t>
+          <t>investment_country</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v3</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>openfigi.security.v3</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -736,17 +736,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>share_class</t>
+          <t>issuer_type</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>sec.thirteenf.information_table.security.v1</t>
+          <t>sec.nport.security.v2</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -763,25 +763,187 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>market_sector</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v3</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>name_of_issuer</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v3, sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>restricted</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>security_type</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v3</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>security_type2</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v3</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>openfigi.security.v3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>share_class</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>sec.thirteenf.information_table.security.v1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/security.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>title_of_class</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>sec.thirteenf.information_table.security.v1, sec.nport.security.v2</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>sec.thirteenf.information_table.security.v1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Kind default</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/security.yaml defaults.sources</t>
         </is>
